--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="479">
   <si>
     <t>Property</t>
   </si>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -472,14 +472,6 @@
   </si>
   <si>
     <t>関連するEncounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2981,10 +2973,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3001,14 +2993,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3030,16 +3022,16 @@
         <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3088,7 +3080,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3117,10 +3109,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3143,13 +3135,13 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3200,7 +3192,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3215,24 +3207,24 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3258,13 +3250,13 @@
         <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3290,14 +3282,14 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="Y13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
       </c>
@@ -3314,7 +3306,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>90</v>
@@ -3329,24 +3321,24 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3369,16 +3361,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3428,7 +3420,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3440,13 +3432,13 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3457,10 +3449,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3483,13 +3475,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3540,7 +3532,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3558,7 +3550,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3569,14 +3561,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3598,13 +3590,13 @@
         <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3654,7 +3646,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3672,7 +3664,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -3683,14 +3675,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3712,16 +3704,16 @@
         <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3770,7 +3762,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3799,10 +3791,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3828,13 +3820,13 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3860,14 +3852,14 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z18" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="Y18" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
       </c>
@@ -3884,7 +3876,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>90</v>
@@ -3902,7 +3894,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -3913,10 +3905,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3939,16 +3931,16 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3998,7 +3990,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>90</v>
@@ -4016,7 +4008,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -4027,10 +4019,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4053,16 +4045,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4088,14 +4080,14 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4112,7 +4104,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>90</v>
@@ -4130,21 +4122,21 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4167,13 +4159,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4224,7 +4216,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4236,13 +4228,13 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4253,10 +4245,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4279,13 +4271,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4336,7 +4328,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4354,7 +4346,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -4365,14 +4357,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4394,13 +4386,13 @@
         <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4450,7 +4442,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4468,7 +4460,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -4479,14 +4471,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4508,16 +4500,16 @@
         <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4566,7 +4558,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4595,10 +4587,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4621,16 +4613,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4656,14 +4648,14 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
       </c>
@@ -4680,7 +4672,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -4698,7 +4690,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -4709,10 +4701,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4735,16 +4727,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4794,7 +4786,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -4812,7 +4804,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4823,10 +4815,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4849,16 +4841,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4884,14 +4876,14 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Y27" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
       </c>
@@ -4908,7 +4900,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4923,24 +4915,24 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4963,13 +4955,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4996,13 +4988,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5020,7 +5012,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5035,24 +5027,24 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5075,13 +5067,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5108,13 +5100,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5132,7 +5124,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5150,25 +5142,25 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5187,16 +5179,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5246,7 +5238,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5261,24 +5253,24 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5301,13 +5293,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5358,7 +5350,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5373,28 +5365,28 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>268</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5413,13 +5405,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5470,7 +5462,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5485,10 +5477,10 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5499,10 +5491,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5525,13 +5517,13 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5582,7 +5574,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5594,27 +5586,27 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5637,13 +5629,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5694,7 +5686,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5712,7 +5704,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5723,14 +5715,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5752,13 +5744,13 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5808,7 +5800,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5826,7 +5818,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5837,14 +5829,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5866,16 +5858,16 @@
         <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5924,7 +5916,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5953,10 +5945,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5979,16 +5971,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6014,14 +6006,14 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6038,7 +6030,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6053,24 +6045,24 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6093,13 +6085,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6150,7 +6142,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6168,21 +6160,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6205,13 +6197,13 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6262,7 +6254,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6277,24 +6269,24 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6317,13 +6309,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6374,7 +6366,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6389,24 +6381,24 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6429,16 +6421,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6488,7 +6480,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6503,24 +6495,24 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6543,16 +6535,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6602,7 +6594,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6617,28 +6609,28 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6657,16 +6649,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6695,10 +6687,10 @@
         <v>114</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6716,7 +6708,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6731,28 +6723,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6771,16 +6763,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6830,7 +6822,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6845,24 +6837,24 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6885,13 +6877,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6942,7 +6934,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6954,13 +6946,13 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6971,10 +6963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6997,13 +6989,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7054,7 +7046,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7072,7 +7064,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7083,14 +7075,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7112,13 +7104,13 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7168,7 +7160,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7186,7 +7178,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7197,14 +7189,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7226,16 +7218,16 @@
         <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7284,7 +7276,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7313,14 +7305,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7339,16 +7331,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7398,7 +7390,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7413,24 +7405,24 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7453,13 +7445,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7489,10 +7481,10 @@
         <v>114</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7510,7 +7502,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7528,7 +7520,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7539,10 +7531,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7565,13 +7557,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7622,7 +7614,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7640,7 +7632,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7651,10 +7643,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7677,16 +7669,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7736,7 +7728,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7754,7 +7746,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7765,10 +7757,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7791,16 +7783,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7850,7 +7842,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7862,13 +7854,13 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -7879,10 +7871,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7905,13 +7897,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7962,7 +7954,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7980,7 +7972,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -7991,14 +7983,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8020,13 +8012,13 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8076,7 +8068,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8094,7 +8086,7 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8105,14 +8097,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8134,16 +8126,16 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8192,7 +8184,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8221,10 +8213,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8247,13 +8239,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8304,7 +8296,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8322,21 +8314,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8359,13 +8351,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8416,7 +8408,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8434,7 +8426,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8445,10 +8437,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8471,13 +8463,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8507,10 +8499,10 @@
         <v>114</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -8528,7 +8520,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8546,21 +8538,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8583,13 +8575,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8616,13 +8608,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8640,7 +8632,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8658,21 +8650,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8695,19 +8687,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8732,13 +8724,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8756,7 +8748,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8774,21 +8766,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8811,13 +8803,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8847,10 +8839,10 @@
         <v>114</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -8868,7 +8860,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8886,21 +8878,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8923,13 +8915,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8959,10 +8951,10 @@
         <v>114</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -8980,7 +8972,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8998,21 +8990,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9035,13 +9027,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9092,7 +9084,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9110,21 +9102,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9147,13 +9139,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9180,13 +9172,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9204,7 +9196,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9222,21 +9214,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9259,16 +9251,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9318,7 +9310,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9330,13 +9322,13 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9347,10 +9339,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9373,13 +9365,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9430,7 +9422,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9448,7 +9440,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -9459,14 +9451,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9488,13 +9480,13 @@
         <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9544,7 +9536,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9562,7 +9554,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9573,14 +9565,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9602,16 +9594,16 @@
         <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9660,7 +9652,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9689,10 +9681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9715,13 +9707,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9772,7 +9764,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>90</v>
@@ -9787,24 +9779,24 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9830,13 +9822,13 @@
         <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9862,13 +9854,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -9886,7 +9878,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9904,7 +9896,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9915,10 +9907,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9941,16 +9933,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9976,13 +9968,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -10000,7 +9992,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10029,10 +10021,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10055,13 +10047,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10112,7 +10104,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10130,7 +10122,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10141,10 +10133,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10167,13 +10159,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10224,7 +10216,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10239,24 +10231,24 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10279,16 +10271,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10338,7 +10330,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10353,10 +10345,10 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
